--- a/results/all_images/summary_all_images.xlsx
+++ b/results/all_images/summary_all_images.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,6 +468,101 @@
           <t>field length density (px^-1)</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>perimeter per cell (px)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ring area 30 px per cell (px^2)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>ring area 60 px per cell (px^2)</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>in-frame fraction 30 px per cell</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>in-frame fraction 60 px per cell</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ring density 30 px per cell (px^-1)</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>ring density 60 px per cell (px^-1)</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>roots per 100 px perimeter per cell</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>ring attached length 30 px per cell (px)</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>ring attached length 60 px per cell (px)</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ring length weighted 30 px per cell (px)</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>ring length weighted 60 px per cell (px)</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Sholl crossings 10 px per cell</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Sholl crossings 20 px per cell</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Sholl crossings 30 px per cell</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>field length density weighted (px^-1)</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>field length density without flagged regions (px^-1)</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>field length density in ROI (px^-1)</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>image_label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -506,6 +601,62 @@
       <c r="J2" t="n">
         <v>0.03465004</v>
       </c>
+      <c r="K2" t="n">
+        <v>297.8123</v>
+      </c>
+      <c r="L2" t="n">
+        <v>10771.6923</v>
+      </c>
+      <c r="M2" t="n">
+        <v>25565.4615</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.9908</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.03275532</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.0350223</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.9437</v>
+      </c>
+      <c r="S2" t="n">
+        <v>273.3077</v>
+      </c>
+      <c r="T2" t="n">
+        <v>501</v>
+      </c>
+      <c r="U2" t="n">
+        <v>408.2629</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1023.9562</v>
+      </c>
+      <c r="W2" t="n">
+        <v>9.7692</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12.5385</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.03903357</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.03451624</v>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>542_z06</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -544,6 +695,62 @@
       <c r="J3" t="n">
         <v>0.03407276</v>
       </c>
+      <c r="K3" t="n">
+        <v>349.6878</v>
+      </c>
+      <c r="L3" t="n">
+        <v>12006.1818</v>
+      </c>
+      <c r="M3" t="n">
+        <v>28554.2727</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.9834000000000001</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.9555</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.02900112</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.03326266</v>
+      </c>
+      <c r="R3" t="n">
+        <v>2.3636</v>
+      </c>
+      <c r="S3" t="n">
+        <v>239.9091</v>
+      </c>
+      <c r="T3" t="n">
+        <v>479.8182</v>
+      </c>
+      <c r="U3" t="n">
+        <v>397.1731</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1090.3199</v>
+      </c>
+      <c r="W3" t="n">
+        <v>9.3636</v>
+      </c>
+      <c r="X3" t="n">
+        <v>13.2727</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>14.8182</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.03838905</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.03399229</v>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>542_z18</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -582,6 +789,62 @@
       <c r="J4" t="n">
         <v>0.04470139</v>
       </c>
+      <c r="K4" t="n">
+        <v>222.1007</v>
+      </c>
+      <c r="L4" t="n">
+        <v>8742.1667</v>
+      </c>
+      <c r="M4" t="n">
+        <v>22189.9167</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.9965000000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.9814000000000001</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.03474981</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.04342795</v>
+      </c>
+      <c r="R4" t="n">
+        <v>3.3871</v>
+      </c>
+      <c r="S4" t="n">
+        <v>232.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>572.8333</v>
+      </c>
+      <c r="U4" t="n">
+        <v>342.9959</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1096.3385</v>
+      </c>
+      <c r="W4" t="n">
+        <v>8.583299999999999</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>14.5833</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.05068186</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.04470139</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>543-2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -620,6 +883,62 @@
       <c r="J5" t="n">
         <v>0.04513983</v>
       </c>
+      <c r="K5" t="n">
+        <v>236.3819</v>
+      </c>
+      <c r="L5" t="n">
+        <v>9046.2222</v>
+      </c>
+      <c r="M5" t="n">
+        <v>22951.3333</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.9957</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.03428217</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.04317158</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.9693</v>
+      </c>
+      <c r="S5" t="n">
+        <v>220.8889</v>
+      </c>
+      <c r="T5" t="n">
+        <v>507.3333</v>
+      </c>
+      <c r="U5" t="n">
+        <v>351.7792</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1119.6164</v>
+      </c>
+      <c r="W5" t="n">
+        <v>7.7778</v>
+      </c>
+      <c r="X5" t="n">
+        <v>13.2222</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.05110365</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.04513983</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>543_3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -658,6 +977,62 @@
       <c r="J6" t="n">
         <v>0.04380241</v>
       </c>
+      <c r="K6" t="n">
+        <v>207.4787</v>
+      </c>
+      <c r="L6" t="n">
+        <v>8447.8182</v>
+      </c>
+      <c r="M6" t="n">
+        <v>21999.7273</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.03624067</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.04402843</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3.2312</v>
+      </c>
+      <c r="S6" t="n">
+        <v>204.6364</v>
+      </c>
+      <c r="T6" t="n">
+        <v>498.3636</v>
+      </c>
+      <c r="U6" t="n">
+        <v>341.9271</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1087.2355</v>
+      </c>
+      <c r="W6" t="n">
+        <v>8.0909</v>
+      </c>
+      <c r="X6" t="n">
+        <v>11.7273</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>14.2727</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.04958231</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.04380241</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>543_z13</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -696,6 +1071,62 @@
       <c r="J7" t="n">
         <v>0.03464652</v>
       </c>
+      <c r="K7" t="n">
+        <v>275.4257</v>
+      </c>
+      <c r="L7" t="n">
+        <v>10379.625</v>
+      </c>
+      <c r="M7" t="n">
+        <v>24427.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.9949</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.03800643</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.04004776</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.538</v>
+      </c>
+      <c r="S7" t="n">
+        <v>317.125</v>
+      </c>
+      <c r="T7" t="n">
+        <v>673.25</v>
+      </c>
+      <c r="U7" t="n">
+        <v>445.9204</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1103.9582</v>
+      </c>
+      <c r="W7" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="X7" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0.03869506</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.03502703</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>682_z08</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -734,6 +1165,62 @@
       <c r="J8" t="n">
         <v>0.03829817</v>
       </c>
+      <c r="K8" t="n">
+        <v>221.5717</v>
+      </c>
+      <c r="L8" t="n">
+        <v>8909.8182</v>
+      </c>
+      <c r="M8" t="n">
+        <v>22488.8182</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.9972</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.03201806</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.0356529</v>
+      </c>
+      <c r="R8" t="n">
+        <v>3.0793</v>
+      </c>
+      <c r="S8" t="n">
+        <v>213.2727</v>
+      </c>
+      <c r="T8" t="n">
+        <v>419.4545</v>
+      </c>
+      <c r="U8" t="n">
+        <v>315.3412</v>
+      </c>
+      <c r="V8" t="n">
+        <v>890.9974</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7.4545</v>
+      </c>
+      <c r="X8" t="n">
+        <v>10.8182</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>13</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.04303411</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.0380563</v>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>682_z23</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -771,6 +1258,62 @@
       </c>
       <c r="J9" t="n">
         <v>0.03748464</v>
+      </c>
+      <c r="K9" t="n">
+        <v>201.3086</v>
+      </c>
+      <c r="L9" t="n">
+        <v>7938.5455</v>
+      </c>
+      <c r="M9" t="n">
+        <v>19815</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.9943</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.03152782</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.03455861</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.8431</v>
+      </c>
+      <c r="S9" t="n">
+        <v>177.2727</v>
+      </c>
+      <c r="T9" t="n">
+        <v>349.3636</v>
+      </c>
+      <c r="U9" t="n">
+        <v>277.0839</v>
+      </c>
+      <c r="V9" t="n">
+        <v>775.4374</v>
+      </c>
+      <c r="W9" t="n">
+        <v>6.2727</v>
+      </c>
+      <c r="X9" t="n">
+        <v>9.454499999999999</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>11.4545</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0.04198674</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.03688309</v>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>682_z29</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -784,7 +1327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,6 +1386,69 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Appended columns (normalised measures, means over interior cells): perimeter; ring area A_r, the pixels</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>of the nearest-lacuna partition within r px of the body; in-frame fraction of the full r px annulus;</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ring density L_r / A_r; roots per 100 px of perimeter. They remove the dependence of roots and ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>length on lacuna size (docs/OVERNIGHT_REPORT.md, task 4.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Appended on branch canaliculi-v2: ring attached length 30 / 60 px, the ring length pixels in threads that</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>reach within 10 px of the lacuna (passing threads left out); ring length weighted 30 / 60 px and field</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>length density weighted, chain code lengths (sqrt(2) per diagonal step); Sholl crossings 10 / 20 / 30 px,</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>skeleton components crossing a 1.5 px band at that distance from the lacuna (no graph); see</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>docs/CANALICULI_V2_REPORT.md.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
